--- a/apps/electron/resources/skills/office-business/cases/household-budget/example.xlsx
+++ b/apps/electron/resources/skills/office-business/cases/household-budget/example.xlsx
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/drawings/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <c:date1904 val="0"/>
   <c:chart>
     <c:title>
@@ -135,7 +135,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Series 1</c:v>
+            <c:v>本期实际</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -216,10 +216,6 @@
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -227,7 +223,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -252,7 +248,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5f21520976d04300"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3d570c086ca640ef"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -371,7 +367,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:pageSetUpPr fitToPage="1"/>
   </x:sheetPr>
@@ -580,6 +576,6 @@
     </x:row>
   </x:sheetData>
   <x:pageSetup fitToWidth="1" fitToHeight="1" orientation="landscape"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27b98f3c2e194c18"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20a32db3898d4365"/>
 </x:worksheet>
 </file>